--- a/Database/exercises_database.xlsx
+++ b/Database/exercises_database.xlsx
@@ -363,7 +363,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mv="urn:schemas-microsoft-com:mac:vml">
-  <dimension ref="A1:A28"/>
+  <dimension ref="A1:A29"/>
   <sheetData>
     <row r="1" spans="1:1" customFormat="false">
       <c r="A1" s="0" t="str">
@@ -492,16 +492,21 @@
     </row>
     <row r="26" spans="1:1" customFormat="false">
       <c r="A26" s="0" t="str">
-        <v>Teres Major</v>
+        <v>Soleus</v>
       </c>
     </row>
     <row r="27" spans="1:1" customFormat="false">
       <c r="A27" s="0" t="str">
-        <v>Triceps Brachii</v>
+        <v>Teres Major</v>
       </c>
     </row>
     <row r="28" spans="1:1" customFormat="false">
       <c r="A28" s="0" t="str">
+        <v>Triceps Brachii</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" customFormat="false">
+      <c r="A29" s="0" t="str">
         <v>Upper Traps</v>
       </c>
     </row>
